--- a/artfynd/A 56530-2023 artfynd.xlsx
+++ b/artfynd/A 56530-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56530-2023 artfynd.xlsx
+++ b/artfynd/A 56530-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81562055</v>
+        <v>129848217</v>
       </c>
       <c r="B2" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>2668</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alingsås, Vg</t>
+          <t>Bolltorp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356646.9482984419</v>
+        <v>356690</v>
       </c>
       <c r="R2" t="n">
-        <v>6425390.79220986</v>
+        <v>6425624</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,32 +739,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Naturvärdesinventering på uppdrag av Alingsås kommun. Calluna AB (EEN0011).</t>
+          <t>Måttliga förekomster</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Gabriella Samuelsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Gabriella Samuelsson, Anna Sjövall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +784,7 @@
         <v>107683270</v>
       </c>
       <c r="B3" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356686.079870309</v>
+        <v>356686</v>
       </c>
       <c r="R3" t="n">
-        <v>6425472.792893318</v>
+        <v>6425473</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +858,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107683570</v>
+        <v>107683561</v>
       </c>
       <c r="B4" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,31 +907,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -971,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>356612.1797143526</v>
+        <v>356534</v>
       </c>
       <c r="R4" t="n">
-        <v>6425282.071155953</v>
+        <v>6425273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,19 +978,14 @@
           <t>2022-03-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-03-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kiande några ggr, hanen sågs sedan födosökande i alar. Efter en stund ses även en hona födosökande precis intill, som bitvis gör små kontaktläten, så troligen ett par. Även honan kiande en gång. Hanen sågs sen flyga över ån, honan kvar. Många tidigare hål i alarna här.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107682497</v>
+        <v>107682925</v>
       </c>
       <c r="B5" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>102999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,11 +1049,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
@@ -1101,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>356623.8775876687</v>
+        <v>356746</v>
       </c>
       <c r="R5" t="n">
-        <v>6425326.276628424</v>
+        <v>6425619</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,22 +1090,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1166,7 +1115,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Edvardsson</t>
+          <t>Per Österman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1177,37 +1126,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107683545</v>
+        <v>107682496</v>
       </c>
       <c r="B6" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1215,9 +1159,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1226,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>356697.5466600358</v>
+        <v>356684</v>
       </c>
       <c r="R6" t="n">
-        <v>6425480.881541764</v>
+        <v>6425489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,22 +1205,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,37 +1241,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107683560</v>
+        <v>107682497</v>
       </c>
       <c r="B7" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1340,9 +1274,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1351,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>356532.6864833609</v>
+        <v>356624</v>
       </c>
       <c r="R7" t="n">
-        <v>6425247.203178253</v>
+        <v>6425326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,22 +1320,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,19 +1356,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107682496</v>
+        <v>107682516</v>
       </c>
       <c r="B8" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1465,11 +1389,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1481,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>356683.4610167474</v>
+        <v>356501</v>
       </c>
       <c r="R8" t="n">
-        <v>6425488.823496731</v>
+        <v>6425201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,7 +1425,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1514,19 +1433,9 @@
           <t>2022-05-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,15 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107682944</v>
+        <v>81562055</v>
       </c>
       <c r="B9" t="n">
-        <v>57068</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,16 +1477,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103057</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1590,29 +1494,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Alingsås, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>356636.2378877981</v>
+        <v>356647</v>
       </c>
       <c r="R9" t="n">
-        <v>6425344.427041952</v>
+        <v>6425391</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1636,22 +1531,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering på uppdrag av Alingsås kommun. Calluna AB (EEN0011).</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,15 +1556,668 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>107683545</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Alingsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>356698</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6425481</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Marlijn Sterenborg</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>107683560</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Alingsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>356532</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6425247</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>90008897</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Alingsås Norr, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>356552</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6425201</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-06-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fågelinventering på uppdrag av Alingsås kommun. Calluna AB (EEN0025).</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>107683558</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Alingsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>356518</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6425235</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>107683570</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Alingsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>356612</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6425282</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-03-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>107682944</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Alingsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>356636</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6425344</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Per Österman</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>

--- a/artfynd/A 56530-2023 artfynd.xlsx
+++ b/artfynd/A 56530-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129848217</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107683270</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107683561</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107682925</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107682496</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107682497</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107682516</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81562055</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107683545</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107683560</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90008897</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2002,6 +2062,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107683558</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2112,6 +2177,11 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107683570</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2222,8 +2292,29 @@
           <t>MHT0289_Alingsås_fågelinventering_2022_(CallunaAB)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107682944</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>